--- a/export_2026-06-10_split.xlsx
+++ b/export_2026-06-10_split.xlsx
@@ -1960,6 +1960,133 @@
           <t>3w_TusboGVo</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[Music]
+ Are you curious about what goes into the media that nour
+ishes yourselves?
+ Ever wondered how the choice of components could make or
+ break your experiment?
+ In this video, we'll explore the key components of cell
+ culture media and how to select
+ the best option for your specific cell types.
+ Cell culture media provides the nutrients and environment
+ that your cells need to grow
+ and function.
+ Choosing the right media is critical because it directly
+ impacts cell growth and the overall
+ success of your experiments.
+ Each type of cell has unique needs, so it's essential that
+ the media you select is well
+ matched.
+ Let's start with the basal medium.
+ This serves as the foundation of your media, offering the
+ essential environment your
+ cells need.
+ Typical basal medium contains amino acids like alglutamine,
+ which support proteins synthesis,
+ a vital process for cell growth.
+ You'll also find vitamins such as vitamin B and C, which
+ help with cell division and
+ energy production.
+ Additionally, minerals like calcium, magnesium, potassium
+ and sodium are crucial for cell
+ adhesion and function.
+ Glucose is another key component, providing the energy your
+ cells need for growth.
+ Cell types of basal media are commonly used in labs, each
+ tailored to different cell
+ types.
+ For example, Dolbeco's modified eagle medium, or DMEM, is
+ rich in amino acids, vitamins and
+ glucose, making it ideal for cultureing a variety of mammal
+ian cells, especially the adherent
+ cells with fast growth and low adhesion.
+ RPMI 1640 is another popular choice, known for its wide
+ range of amino acids, vitamins and
+ inorganic salts, and is commonly used for cultureing lymph
+oid cells, hyperdomas, and hematopoeatic
+ cells.
+ If you're working with adherent cell lines like fiberglass,
+ you might turn to minimum
+ essential medium, or MEM, which is designed with essential
+ amino acids, vitamins, and glucose
+ to meet their needs.
+ For those cultureing CHO cells, Hams F, 12 nutrient mixture
+, is a go-to, offering a broad
+ spectrum of amino acids, vitamins, and lipids.
+ And then there's McCoy's 5A medium, which is particularly
+ well-suited for primary and
+ established cell lines, especially fiberglass, thanks to
+ its rich content of amino acids and
+ vitamins.
+ Now that we've covered the basal medium, let's move on to
+ another critical component,
+ serum, which is like the lifeblood of cell culture.
+ It supplies growth factors, hormones, and nutrients that
+ help cells proliferate.
+ Real bovine serum, FBS, is widely used because of its
+ ability to support a range of cell
+ types.
+ It contains vital elements like insulin for glucose
+ metabolism and transparent for iron transport.
+ serum also helps buffer the medium, protecting cells during
+ handling.
+ However, since it's a natural product, its composition can
+ vary, making consistency important.
+ serum also plays a detoxifying role by binding and neutral
+izing potential toxins that
+ could harm cells.
+ This makes it an indispensable component in many protocols,
+ particularly for primary cells
+ or sensitive cell types.
+ Aside from FBS, other types of serum like equine serum are
+ sometimes used for cultureing
+ cells that need different growth factors or are sensitive
+ to components found in FBS.
+ Once your basal medium and serum are in place, you'll need
+ to ensure a stable environment
+ with the right buffering system.
+ FBS helps maintain a stable pH, which is critical for cell
+ growth.
+ The most common buffer is bicarbonate, which works
+ alongside CO2 in the incubator to maintain
+ pH balance.
+ If you're working in open-air systems or outside of incub
+ator, you might use heps, which
+ offers broader pH stability.
+ In addition to stabilizing pH, buffers can also help
+ mitigate the effects of metabolic
+ byproducts that cells produce as they grow.
+ For instance, lactic acid is a common byproduct of cellular
+ metabolism that can lower the
+ pH of the medium.
+ A well-chosen buffer system can neutralize these acids,
+ preventing potentially harmful shifts
+ in pH that could compromise cell viability and function.
+ Finally, let's consider antibiotics and supplements.
+ Antibiotics, such as penicillin and struptolycin, are often
+ added to prevent contamination.
+ While helpful, they should be used carefully as overalience
+ can mass contamination issues.
+ Supplements like insulin and transparent are also key in
+ supporting specific cell needs.
+ Some cells may require specialized supplements, such as non
+-essential amino acids, NEA or
+ antioxidants, to reduce metabolic stress and protect
+ against damage.
+ By choosing the right combination of basal medium, serum,
+ buffers and supplements, you create
+ an environment where your cells can thrive.
+ Understanding these components allows you to tailor your
+ media for better results in your
+ experiments.
+ That's all for today.
+ If you found this video helpful, don't forget to like and
+ subscribe for more insights.
+ Thanks for watching, and I'll see you in the next video.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2015,6 +2142,144 @@
           <t>0HHY4F5uAqA</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[Music]
+ Having the right equipment and materials in your cell
+ culture lab is essential.
+ Without a clear understanding of what you need,
+ you risk running into issues like missing crucial tools at
+ critical moments.
+ In this video, we'll guide you through the essential
+ equipment and materials you need for your cell culture lab,
+ explaining what they are and how they function in your
+ experiments.
+ By the end, you'll have a clear understanding of what's
+ required to set up your lab and avoid unnecessary disrupt
+ions during your research.
+ If this sounds like what you need, stay with us as we
+ explore these essentials and detail.
+ First up, let's start with a backbone of any cell culture
+ lab, the biological safety cabinet or BSC.
+ Its main function is to create a sterile workspace,
+ protecting your samples from contamination by filtering the
+ air through hepatophilters.
+ This ensures that the environment inside the cabinet
+ remains clean, safeguarding your cells from bacteria, fungi
+, and other airborne contaminants.
+ In cell culture experiments, the BSC is used whenever you
+ handle cells, prepare culture media, or perform sterile
+ techniques.
+ By working within the BSC, you minimize the risk of
+ introducing contaminants that could compromise your
+ experiments.
+ With the BSC covered, let's shift our focus to another
+ critical piece of equipment that keeps your cells happy and
+ thriving.
+ The CO2 incubator.
+ The CO2 incubator plays a vital role in maintaining optimal
+ growth conditions for your cells.
+ Its main function is to control the environment by
+ regulating temperature, humidity, and CO2 levels, creating
+ conditions that closely mimic the heat.
+ The CO2 can be used in a single cell, which is a very
+ important function for the cell to be used in a single cell
+.
+ The CO2 helps maintain the correct pH of the culture media,
+ while the system temperature and humidity keep the cells
+ healthy and prevent dehydration.
+ Moving on, it's time to talk about a tool that gives you a
+ closer look at your cells.
+ The microscope.
+ Without it, you'd be navigating in the dark.
+ The microscope is essential for observing your cells,
+ checking their health, and ensuring they're growing as
+ expected.
+ In cell culture, an inverted microscope is typically used
+ as it allows you to view cells at the bottom of flasks or
+ dishes without disturbing them.
+ Microscopes help you monitor cell morphology, identify
+ contamination early, and assess cell viability, giving you
+ real-time feedback on how your experiment is progressing.
+ When working with live cells, features like phase contrast
+ are particularly useful, enhancing the visibility of
+ transparent cells without needing to stain them.
+ Let's spin into our next essential. The centrifuge. A work
+horse for any cell culture lab.
+ The centrifuge is crucial for separating components based
+ on density, which is a key step in many cell culture
+ procedures.
+ It's used for pelleting cells, washing them, and preparing
+ samples for further analysis or media changes. By spinning
+ samples at high speeds, the centrifuge forces cells or
+ other particles to the bottom of the tube, making them easy
+ to collect or discard.
+ In cell culture experiments, the centrifuge ensures
+ efficient cell recovery during passaging helps in removing
+ excess media and is vital when concentrating cells for
+ downstream applications.
+ Beyond the core equipment, there are a few more key players
+ that keep your lab running smoothly. Let's take a quick
+ look at these vital tools.
+ Water bath is used for warming up media, reagents, and th
+ong frozen cells. It ensures your samples are at the correct
+ temperature before use, preventing thermal shock to your
+ cells.
+ Autoclave is your godo for sterilizing glassware, pipettes,
+ and other reusable items, effectively eliminating any
+ potential contaminants before they come into contact with
+ your samples.
+ Refridgerator and freezer are crucial for storing culture
+ media, reagents, and preserving samples. Keeping your
+ materials at the correct storage conditions ensures their
+ longevity and performance in your experiments.
+ Puppettes and pipettes are essential for accurately
+ measuring and transferring liquids.
+ Precision is key in cell culture, and having the right pip
+ettes helps maintain the integrity of your experiments.
+ Of course, no cell culture lab is complete without the
+ consumables and reagents that make your experiments
+ possible.
+ Here's a sneak peek at what you'll be working with every
+ day.
+ Cell culture media and reagents are the lifeblood of your
+ cells, providing them with the nutrients and conditions
+ they need to thrive.
+ This includes everything from basal media to essential
+ supplements like fetal bovine serum, FBS, and antibiotics.
+ You'll also be working with various flasks, dishes, and
+ plates. These are your primary vessels for growing and
+ maintaining cells, available in various formats to suit
+ different experimental needs.
+ Serological pipettes and tips are essential for sterile
+ liquid handling, ensuring precision in every step of your
+ cell culture workflow.
+ Cryogenic vials and storage solutions are for safely
+ preserving your cells, especially when long-term storage is
+ required.
+ To keep your lab environment safe and contamination free,
+ let's briefly cover some essential maintenance and safety
+ materials.
+ Disinfectants and sterilization materials such as 70%
+ ethanol, bleach, UV sterilizers, and sterile wipes and
+ sprays are vital for maintaining a sterile environment and
+ preventing cross contamination.
+ Personal protective equipment such as gloves, lab coats,
+ and eye protection.
+ Keeps you safe while handling hazardous materials, making
+ sure you can work confidently in your lab.
+ That wraps up our guide to the essential equipment and
+ materials for setting up your cell culture lab.
+ Each tool plays a crucial role in your research and knowing
+ how they function can make all the difference.
+ If you found this helpful, don't forget to subscribe, like,
+ and follow us for more insights.
+ We've got plenty of deep dives on these topics coming up,
+ so stay tuned.
+ You won't want to miss what's next.
+ (gentle music)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2070,6 +2335,117 @@
           <t>WllvWfcf5PI</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[Music]
+ Ever had a cell culture ruined by contamination?
+ Or maybe you've wondered if you're doing enough to keep
+ your experiment sterile?
+ In today's video, we're going to cover the essentials of
+ sterile technique
+ and cell culture step-by-step from prepping your workspace
+ to handling cells.
+ By the end, you'll know exactly how to avoid contamination
+ every step of the way.
+ Let's start by talking about why sterility matters.
+ You might think it's just about keeping things clean, but
+ it's really about ensuring the integrity of your results.
+ When we culture cells, we're creating a perfect environment
+ for all kinds of organisms to grow.
+ Bacteria, fungi, yeast, even tiny contaminants like micop
+lasma.
+ And if any of those get into your culture, it can change
+ your results, waste your time, and set you back days, or
+ even weeks.
+ So, following sterile techniques protects your experiment
+ and gives you confidence that your data is reliable.
+ Alright, now let's get into what you need to do before you
+ even start the experiment.
+ First, personal preparation.
+ Make sure you're wearing a clean lab coat, gloves, and a
+ heronet.
+ It might sound obvious, but these basics are your first
+ line of defense against contamination.
+ And avoid wearing any jewelry, or make up, that could shed
+ particles into the workspace.
+ Next, let's talk about setting up your workspace.
+ Disinfect your biological safety cabinet with UV light for
+ 30 minutes.
+ Ensure all surfaces are adequately exposed.
+ A cluttered space is just asking for contamination, so keep
+ things organized.
+ Arrange everything you'll need, like pippets, media bottles
+, and tools, with an easy reach to avoid unnecessary
+ movement.
+ And lastly, preparation of your equipment and reagents.
+ Wipe down all bottles, flasks, and tools with ethanol
+ before they even enter the cabinet.
+ Pre-label any media and solutions too. Trust me, you don't
+ want to realize halfway through that you need to write
+ something down.
+ Now, let's go through each stage of the cell culture
+ process and look at what sterile techniques to use at each
+ step.
+ Step 1. Media preparation. When you're preparing media, the
+ first rule is to keep everything as sterile as possible.
+ Wipe down the media bottles and reagent containers before
+ placing them inside the cabinet.
+ Use fresh, sterile pipette tips for each reagent, so you
+ don't risk cross-contaminating them, and be mindful when
+ opening bottles.
+ Only open them as much as you need, and avoid putting caps
+ down on any surfaces.
+ Step 2. Preparing the flask or dish for cell culture. Once
+ you're ready to work with your flask or dish, place it
+ inside the sterile area of the cabinet,
+ and avoid putting it right near the edges where
+ contamination risk is higher.
+ If you need to remove a cap or lid, hold it or place it
+ upside down on a sterile surface to keep it clean.
+ Step 3. Adding media to the flask. When you're adding media
+ to your flask, make sure you're using proper pepetting
+ techniques.
+ Avoid touching the sides of the flask with a pepette tip,
+ and control the angle and depth carefully, so you don't end
+ up splashing media around.
+ And as always, use a fresh tip for each different reagent
+ to avoid cross-contamination.
+ Step 4. Handling cells and adding them to media.
+ Now, when it's time to add your cells to the culture media,
+ use a septic pepetting.
+ Be extra careful here because this is where even a minor
+ contamination can ruin the entire culture.
+ Handling yourself containers and pepets carefully, and
+ avoid passing your hands directly over open containers.
+ This helps reduce the risk of airborne contamination.
+ Step 5. Incubation and monitoring. When you're ready to
+ incubate, carefully transfer your flask or dish to the
+ incubator.
+ Make sure the incubator is clean and regularly disinfected,
+ especially the internal surfaces.
+ Keep an eye on it during your experiment to ensure nothing
+ unexpected is growing.
+ Step 6. Post experiment clean up.
+ And finally, let's talk about cleaning up.
+ Dispose of any waste immediately and appropriately.
+ Don't leave anything sitting around that could become a
+ contamination risk.
+ Wipe down all surfaces in the cabinet with 70% ethanol one
+ last time, and then expose the cabinet to UV light for 30
+ minutes.
+ As you remove your gloves and lab coat, be careful not to
+ spread any contaminants outside the BSC.
+ So, that's it. Those are the essential steps to keep your
+ cell culture experiment sterile.
+ It might feel like a lot at first, but once you get into
+ the habit of following these steps, it'll become second
+ nature.
+ Stick with these habits, and you'll be able to trust your
+ results and avoid setbacks.
+ Thanks for watching, and I hope these tips help keep your
+ cultures clean and your experiments running smoothly.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2125,6 +2501,79 @@
           <t>b--J2uvy8HU</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[Music]
+ Have you ever wondered why it's so important to choose the
+ right type of cell culture for your experiments?
+ Well, understanding the difference between adherent and
+ suspension cells is more than just a technical detail.
+ It can make a big difference in your research quality,
+ prevent costly setbacks, and save you a lot of time and
+ effort down the line.
+ So let's break it down. So you're set up for success from
+ day one.
+ First, let's talk about where each cell type really shines.
+ adherent cells are your go-to for studies that need a
+ structured environment,
+ think tissue engineering, cancer research, and cellular
+ response studies.
+ They stick to a solid surface, forming a layer that mimics
+ the organized structure of tissues in the body.
+ This setup is ideal for studying things like cell shape,
+ movement, and interaction, which is why you'll see adherent
+ cultures heavily used in drug discovery and toxicology
+ studies.
+ However, if your work calls for large cell numbers or
+ scaling up production, suspension cells might be a better
+ fit.
+ These cells float freely in the medium and don't rely on
+ any surface for growth.
+ This makes them perfect for applications that require high
+ cell density, like antibody production, high throughput
+ screening, or recombinant protein manufacturing.
+ Plus, suspension cells are easy to transfer to bioreactors,
+ which is a huge advantage when you're working on a large
+ scale.
+ Once you've picked the right cell type, keeping them
+ healthy is key.
+ Both cell types need regular subculturing to stay active,
+ but the process is a bit different for each.
+ For adherent cells, subculturing involves a few more steps.
+ These cells stick to surfaces, so you'll need an enzymatic
+ treatment, typically tripsin, to gently detach them.
+ After that, you resespend them in fresh medium, which stops
+ the enzyme action and keeps the cell safe for continued
+ growth.
+ Timing is important here, too much exposure to tripsin can
+ damage the cells, so precision is essential.
+ For suspension cells, the process is pretty straightforward
+.
+ Start with a cell count, then take the needed amount of
+ suspension.
+ After a quick spend to remove the old medium, resespend the
+ cells in fresh medium, adjusting the concentration as
+ needed.
+ Finally, transfer the cells to a new flask, and that's all
+ there is to it.
+ So, to sum it all up, adherent cells are great for studies
+ that need structured, tissue-like environments, while
+ suspension cells are your best bet for scalable, high-d
+ensity applications.
+ Knowing these distinctions helps you match your cell
+ culture type with a specific demands of your research,
+ which can make a huge difference in your results.
+ Thanks so much for watching!
+ If you found this video helpful, don't forget to give it a
+ thumbs up, subscribe to our channel, and hit that
+ notification bell so you never miss an update.
+ We've got plenty more content coming your way, packed with
+ tips, insights, and deep dives to support your research
+ journey.
+ So stay tuned, and let's keep exploring together.
+ See you in the next video!</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2180,6 +2629,124 @@
           <t>0BlRBEPHcHo</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>[Music]
+ Welcome to today's video. Calculations are the backbone of
+ successful cell culture experiments.
+ Whether it's preparing media, seating cells, or scaling up
+ cultures, getting the math right
+ insures consistent results. In this video, we'll simplify
+ these calculations, provide examples,
+ and finish with practice problems to boost your confidence.
+ Let's start with a basics. Calculating
+ cell concentration and viability. These two go hand in hand
+ when working with a hemocytometer
+ and tripan blue standing. First, to calculate cell
+ concentration, use this formula. Cell concentration
+ equals the average number of cells counted per square
+ multiplied by the delusion factor,
+ multiplied by 10 to the power of 4. This gives you the
+ total number of cells in one
+ milliliter of suspension. Easy, right? Let's try an example
+. Say you counted an average of 50 cells
+ per square and you deluded your sample one to two. Plugging
+ into the formula. 50 times 2 times 10
+ to the power of 4 equals 1 million cells per milliliter.
+ Pretty straightforward. Now let's talk about
+ viability. To calculate cell viability as a percentage,
+ here's what you do. Divide the number of
+ live cells by the total number of cells counted, then
+ multiply by 100. For example, if you counted
+ 120 live cells and 30 dead cells, that's a total of 150
+ cells. So 120 divided by 150 multiplied by
+ 100 gives you 80 percent viability. Not bad. Next up, let's
+ talk about seeding density.
+ Seating density is basically how many cells you want to
+ plate in a specific area or volume.
+ Don't worry, it's easier than it sounds. Here's the formula
+ you need.
+ Volume to seed in milliliters equals the desired cell
+ number divided by the cell concentration.
+ Okay, let's try an example. Say you want one million cells
+ per well and your cell suspension
+ has a concentration of 2 million cells per milliliter.
+ Using the formula, you divide 1 million by
+ 2 million. That gives you 0.5 milliliters. So you need to
+ pipette 0.5 milliliters of your
+ cell suspension into the well. Remember, always double
+ check your math to make sure you're
+ plating the right number of cells. Oh, and one more thing.
+ When you're seeding cells,
+ make sure to mix your cell suspension well. So every pip
+ette pull has the same concentration.
+ Now, let's move on to media preparation and essential part
+ of any cell culture experiment.
+ Don't worry, the math here is pretty simple. You just need
+ this formula.
+ The concentration of the stock solution multiplied by its
+ volume equals the concentration
+ of the final solution multiplied by its volume or more
+ simply. See one times v1 equals c2 times v2.
+ Let's break it down with an example. Say you need 500 mill
+iliters of 10 percent
+ of vs in your culture medium, but your fbs stock is 100%.
+ To calculate how much fbs to add,
+ divide the desired concentration multiplied by the desired
+ volume by the stock concentration.
+ So, that's 10 times 500 divided by 100. The answer is 50
+ milliliters of fbs. Now,
+ subtract that 50 milliliters from the total volume of 500
+ milliliters. You'll need to add 450
+ milliliters of your basal medium to make the final solution
+ make sense? Excellent. Let's move on.
+ Now, let's dive into scaling up cultures. This comes in
+ handy when you need more cells for an
+ experiment or a larger batch. Don't worry, it's not
+ complicated. Here's the formula.
+ Volume to seed equals the desired cell number divided by
+ the cell concentration. Here's an example.
+ Say you're transferring to a 175 square centimeter flask
+ and you need 5 million cells.
+ Your cell suspension has a concentration of 1 million cells
+ per milliliter. Just divide 5 million by
+ 1 million. That's 5 milliliters of cell suspension. Finally
+, let's talk about cell dissociation and
+ subculturing. A routine yet essential part of cell culture.
+ When your cells grow too crowded,
+ you'll need to split them into new flasks. Here's a handy
+ formula for split ratios. Split ratio
+ equals the volume of the old culture divided by the total
+ volume after splitting. Let's go through an
+ example. If you have 10 milliliters of cells in your flask
+ and you want to split them 1 to 5,
+ simply multiply your initial volume by 5. This gives you 50
+ milliliters. So, you'll add 40 milliliters
+ of fresh medium to your 10 milliliters of cells. That's it.
+ You've split your cells 1 to 5.
+ See how that works? Now it's your turn. Let's try some
+ practice problems together.
+ 1. You counted 80 cells per square on average with a 1 to 2
+ delusion. What's the cell
+ concentration in cells per milliliter? 2. You're preparing
+ 250 milliliters of 10% fbs from a 100% stock.
+ How much fbs and medium do you need to mix? 3. If you have
+ 15 milliliters of cell
+ suspension and want to split it 1 to 4. What's the total
+ volume and how much fresh medium do you
+ need to add? Take a moment to solve these. Feel free to
+ pause the video if needed.
+ When you're ready, let us know your answers in the comment
+ section. And that's a wrap.
+ Today, we covered essential calculations for cell culture,
+ including cell concentration,
+ seeding density, media preparation, scaling up and
+ suffering. Mastering these will elevate
+ your lab skills. If you found this helpful, like and
+ subscribe for more lab tutorials.
+ Thanks for watching and happy culture!</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2235,6 +2802,110 @@
           <t>4BgUaM4km3g</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>[Music]
+ Hey everyone, welcome back.
+ If you're working with cells, you know how crucial
+ subculturing is.
+ It's a key process to ensure your
+ cultures stay healthy and continue growing.
+ In this video, we're going to break down the
+ what, when and how of subculturing, so you
+ can confidently handle this essential step.
+ Let's dive in.
+ First, let's start with the basics.
+ What is subculturing?
+ Simply put, subculturing involves transferring
+ cells from one vessel to another.
+ This process helps prevent overcrowding and ensures
+ that the cells have enough space and nutrients to keep
+ growing.
+ Without regular subculturing, cells can become
+ overconfluent, leading to stress, poor growth, or even cell
+ death.
+ When cells are in an optimal environment with plenty of
+ space,
+ they continue growing helpfully and out of controlled rate.
+ Subculturing ensures that your cells remain in this ideal
+ state.
+ Now that we know what subculturing is, let's talk about
+ when to do it.
+ The key indicators are fairly straightforward and
+ understanding them will help
+ you maintain productive cultures.
+ One of the main signs is confluency.
+ When cells reach around 70 to 90% confluency, they're ne
+aring
+ the end of the log phase, where they've been actively
+ growing.
+ This is the ideal time to subculture because overcrowding
+ can slow growth
+ and lead to cell stress.
+ Another indicator is a change in the medium color.
+ As cells metabolize nutrients, the medium's pH can drop,
+ turning it yellow.
+ If you notice this, it's a sign that the cells need fresh
+ medium
+ and more space.
+ Now that you know when to subculture, let's go over how to
+ do it,
+ step by step, so you can follow along and see exactly
+ how to perform the procedure.
+ First, check if the cells have settled at the bottom
+ of the culture flask.
+ If they have, gently rotate the flask to evenly distribute
+ the cells
+ throughout the medium.
+ Next, take a small sample of the cell's suspension
+ and perform a cell count.
+ This will help you calculate how much fresh medium you'll
+ need
+ for subculturing.
+ Now let's look at two methods for subculturing cells.
+ Method one, direct medium addition and splitting.
+ Add the appropriate amount of pre-wormed growth medium
+ to the culture flask.
+ The amount should be based on the total cell number.
+ If you're splitting the culture into multiple flasks,
+ divide the cells accordingly.
+ Loose in the cap of the flask to allow for gas exchange
+ or use a vented cap.
+ Place the flask back into the incubator
+ for continued culture.
+ Method two, centrifugation and medium exchange.
+ Transfer the cell suspension into a 15-millimeter
+ sterile centrifuge tube, centrifuge at 1200 rpm
+ for three minutes after centrifugation.
+ Discard the supernatant and resespend the cell pellet
+ in an appropriate volume of pre-wormed complete growth
+ medium.
+ Based on your cell count, dilute the suspension
+ and transfer the required volume into new culture vessels.
+ Loose in the cap and return the culture to the incubator.
+ For those of you working with adherence cells,
+ there are a few additional steps
+ in the subculturing process.
+ These cells require detachment from the culture surface
+ before they can be transferred.
+ This usually involves using trips in
+ or another dissociation agent to gently detach the cells
+ once detached, the cells are typically neutralized
+ with serum containing medium and resespended
+ before being split into new flasks.
+ If you need a more detailed protocol
+ or step-by-step video for adherence cell subculture,
+ feel free to leave a comment or reach out to us.
+ We'd be happy to share more resources
+ and guide you through the process.
+ That's a wrap on today's subculturing guide.
+ We hope you found this helpful and are ready
+ to implement these techniques in your own work.
+ If you liked the video, don't forget to like,
+ subscribe and follow us for more content like this.
+ Thanks for watching and I'll see you next time.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2290,6 +2961,101 @@
           <t>VDq3uAMdwrQ</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>[Music]
+ Hi everyone! Welcome back to Cell Culture 101. Today we're
+ going to talk about something that's
+ absolutely essential for successful experiments. How to
+ seed cells evenly. Now this might
+ sound simple but trust me, getting an even distribution of
+ cells is one of those foundational
+ skills that can make or break your results. An even seeding
+ can lead to all sorts of headaches
+ overcrowded spots, sparsaries, and even biostata. So if you
+'ve ever wondered how to avoid these
+ issues, you're in the right place. Before we jump into the
+ actual process of seeding, let's take
+ a moment to talk about the cell culture containers we
+ typically use. You've probably worked with
+ T-flasks, Petri dishes, or multi-well plates, right? Each
+ of these has a specific surface area,
+ and because of that, the volume of media and the number of
+ cells you seed need to be adjusted
+ accordingly. For example, A-t-25 flask has a surface area
+ of 25 square centimeters, and you
+ typically add about 5 milliliters of media and seed around
+ 1.25 million cells. On the other hand,
+ if you're working with a 6-well plate, each will has a much
+ smaller area, just 9.6 square centimeters,
+ so you'd only need 2 to 3 milliliters of media and about 4
+80,000 cells. Does that make sense?
+ Essentially, for each container, there's a sweet spot for
+ how much media to add and how many cells
+ to seed. Too much or too little, and you're setting
+ yourself up for uneven growth.
+ I've included a quick cheat sheet for the most commonly
+ used containers, so feel free to pause,
+ and take a closer look if you need to. And here's another
+ thing. It's not just about the numbers.
+ Cell size also matters. If you're working with larger cells
+, you might need to seed fewer of them,
+ and if they're smaller, you might need to adjust upwards.
+ The key here is to observe your cells
+ and tweak the seeding density as needed. Like I said, there
+'s a sweet spot, but you have to make
+ small adjustments depending on the type of cells you're
+ working with. All right, so now that we've
+ covered the basics, let's get into the actual process of
+ seeding cells. How do you make sure they're
+ spread out evenly? Well, the first thing to focus on is
+ your cell suspension. You want to make
+ sure it's properly resistended before you start preparing.
+ If you've ever seen clumps of cells
+ floating around, that's a big red flag. To fix that, simply
+ put it up and down gently. Don't rush it.
+ This breaks up any clumps, and ensures you've got a nice,
+ uniform suspension. Next, remember to mix
+ your cell suspension between each preparing step. This is
+ especially important if you're working with
+ a multi-well plate. Cells have this annoying tendency to
+ settle at the bottom of the tube,
+ and if you're not mixing regularly, your first few wells
+ might end up with too many cells,
+ while the last ones are almost empty. A quick swirl or
+ gentle-puppet, mix can save you from
+ that hassle. Now, when you're actually preparing into your
+ dish or a well plate, take it slow.
+ Don't just squirt the media and like you're in a rush. Move
+ the puppet tip and control its
+ exact or circular motion. This helps spread the cells
+ across the surface evenly. And once you're
+ done, there's a simple trick. Gently tap the plate or a fl
+ask side to side. Not too hard, though,
+ you don't want to slosh media everywhere. This little tap
+ helps the cells settle evenly before you
+ put them in the incubator. Finally, it's always a good idea
+ to check under the microscope after you've
+ seated your cells. Take a quick look at a few wells or
+ dishes and see how things look. If you notice
+ uneven distribution, you can fix it early before the cells
+ attach to the surface. It's a small step,
+ but it can save you a lot of trouble later on. And that's
+ it. Seating cells evenly isn't as complicated
+ as it might seem once you get the hang of it. Just remember
+, start with a good suspension,
+ mix frequently, pipette carefully, and check your work
+ under the microscope. Following these
+ steps will help you get consistent. Reliable results every
+ time. Thank you so much for tuning into
+ today's episode of Cell Culture 101. If you found these
+ tips helpful, make sure to like this video
+ and subscribe for more cell culture tips and tricks. And of
+ course, if you've got your own favorite
+ seating hacks or questions, drop them in the comments below
+. I'd love to hear from you. See you next time.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2345,6 +3111,85 @@
           <t>coZA2-u5Q1s</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>[Music]
+ In cell culture, maintaining and passaging adherence cells
+ requires enzymatic detachment.
+ Tripsinization is a widely used method, but beyond its
+ routine use, understanding its underlying mechanisms is
+ crucial for optimizing experimental outcomes.
+ In this video, we will break down the biochemical
+ principles behind tripsinization, discussing why each step
+ is necessary for ensuring cell viability and reproduci
+bility.
+ It here in cells attached to culture surfaces via integr
+ants, which link them to extracellular matrix proteins.
+ These interactions are stabilized by divalications such as
+ calcium and magnesium.
+ While adhesion is essential for proliferation and function,
+ it poses a challenge when cells need to be passaged or rec
+eded.
+ Tripsinization facilitates detachment by enzymaticly cle
+aving cell adhesion proteins, allowing cells to be
+ transferred and expanded.
+ Tripsin is a serene protease that hydrolyzes peptide bonds
+ in proteins, specifically targeting lysine and arginine
+ residues. By digesting focal adhesion proteins, it disrupt
+ cell attachment to the culture surface.
+ However, the presence of calcium and magnesium stabilizes
+ these adhesion complexes.
+ To enhance tripsin efficiency, EDDA is included in the
+ solution to cellate-divalent cat ions, further destabil
+izing cell adhesion,
+ and making enzymatic cleavage more effective. Before
+ introducing tripsin, cells are typically rinsed with PBS.
+ This step serves two main purposes. First, it removes
+ residual serum, which contains tripsin inhibitors that
+ could prematurely neutralize enzymatic activity.
+ Second, it clears metabolic waste and dead cells, ensuring
+ a more controlled detachment process.
+ Once tripsin is added, incubation at 37 degrees Celsius
+ accelerates proteolytic activity. The duration is critical,
+ insufficient exposure results in incomplete detachment,
+ while prolonged digestion can damage cell surface proteins
+ essential for reattachment and viability.
+ Regular microscopic observation helps determine the optimal
+ endpoint, where cells appear rounded and start to lift from
+ the surface.
+ As tripsin degrades adhesion proteins, cells lose their
+ anchorage, and undergo cytoskeletal reorganization,
+ transitioning from a spread morphology to a rounded shape.
+ This change is a hallmark of successful detachment and can
+ be monitored under a phase contrast microscope.
+ To prevent over digestion, tripsin activity must be
+ promptly inhibited. This can be achieved by adding a
+ complete culture medium containing FBS, which provides
+ protease inhibitors,
+ or by using a dedicated tripsin inhibitor. This step is
+ crucial for preserving cell membrane integrity and ensuring
+ optimal post-possaging recovery.
+ Post-attachment, cell suspensions often contain aggregates
+ that need to be dispersed for accurate seating.
+ Gentle pepating facilitates uniform distribution without
+ inducing excessive shear stress, which can compromise cell
+ viability.
+ The goal is to achieve a single cell suspension while
+ maintaining physiological conditions that support survival
+ and proliferation.
+ Tripsinization is more than just a routine procedure. It is
+ a precisely regulated process that balances enzymatic
+ activity,
+ ionculation, and mechanical handling to maintain cell
+ health.
+ A deeper understanding of these principles allows for
+ better protocol optimization and improved reproducibility
+ in cell culture experiments.
+ Thank you for watching. If you found this discussion
+ insightful, stay tuned for more advanced cell culture
+ techniques and optimization strategies.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2400,6 +3245,109 @@
           <t>y2bbS2pnxPs</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[Music]
+ Cell counting is a critical task in cell culture
+ experiments, essential for ensuring the
+ accuracy and reproducibility of your results.
+ I'll go manually counting cells with a hemocytometer is
+ labor intensive and requires precision.
+ It remains the simplest and most widely adopted method in
+ laboratory settings,
+ particularly when working with a wide variety of cell types
+.
+ Despite the increasing availability of automated cell
+ counters, manual counting continues
+ to be the most practical approach for researchers.
+ In this tutorial, we will focus on the manual counting
+ method, examining the key techniques
+ and steps that ensure accurate results.
+ We'll also cover the vital role of tri-band-blue standing
+ for assessing cell
+ viability and how to calculate cell concentration based on
+ your counts.
+ We're standing these steps will enable you to perform this
+ task with confidence and precision.
+ To begin, it's crucial that the hemocytometer is properly
+ prepared.
+ Ensure that both the cover slip and the chamber are clean
+ and completely dry to avoid
+ sample distortion.
+ Once your sample is loaded, place the hemocytometer under a
+ microscope equipped with a 100x
+ objective lens.
+ This allows you to clearly visualize the grid pattern of
+ the hemocytometer where the cells
+ will be counted.
+ The grid on the hemocytometer is divided into several large
+ squares, and your task is to
+ count the number of cells in a specified number of these
+ squares.
+ For consistency, focus on the four corner squares labeled
+ one, two, four and five.
+ The counting rule is simple but critical.
+ Only count cells that are touching the top and left
+ boundary lines of each square, but
+ exclude cells touching the bottom and right lines.
+ This ensures uniformity across multiple counts and reduces
+ errors.
+ The common challenge during manual counting is cell cl
+umping.
+ If cells are clumped together, treat them as a single unit
+ as it is difficult to accurately
+ distinguish individual cells in a cluster.
+ However, if clumps are large or dense, gently resists bend
+ the cells or even resample
+ to break up the clusters and ensure a more accurate count.
+ Uniform dispersion is crucial for precise cell counting.
+ To accurately assess cell viability, we use tripen blue, a
+ vital stain.
+ Live cells will exclude the die and remain clear, while
+ dead cells will take up the die
+ and a peer blue.
+ For accurate results, mix an equal volume of tripen blue
+ with your cell suspension and
+ incubate for three to five minutes.
+ This will allow sufficient time for the die to penetrate
+ non-viable cells.
+ After counting the cells in the selected grid squares, you
+'ll need to calculate the cell
+ concentration in your original sample.
+ The volume of each large square in the hemisitometer is 0.
+001 milliliters.
+ The formula for determining the total cell concentration in
+ your sample is as follows.
+ This formula provides the number of cells per milliliter of
+ your original sample.
+ The dilution factor accounts for any dilution made during
+ sample preparation, ensuring
+ that your final result accurately reflects the cell
+ concentration in the undiluted sample.
+ An assessing viability with tripen blue, calculate the
+ percentage of viable cells using
+ the formula.
+ Then, to calculate the viable cell concentration per millil
+iter, use.
+ The factor of two is due to the equal volume mixing during
+ tripen blue staining, effectively
+ diluting the sample by half.
+ If tripen blue staining is not performed at a one-to-one
+ ratio, you should calculate the
+ delusion factor based on the actual mixing ratio.
+ In conclusion, manual counting with a hemisitometer remains
+ a reliable and essential technique
+ in a laboratory for determining cell concentration and vi
+ability.
+ While automation offers convenience, manual counting
+ provides researchers with the control
+ needed for precise results, especially in a wide range of
+ applications.
+ By mastering the counting rules and calculation formulas we
+'ve discussed, you'll ensure
+ the accuracy and reproducibility of your experiments.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2455,6 +3403,62 @@
           <t>ZT-DzUq5gIc</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[Music]
+ Cell resuscitation is the first step in cell culture, and
+ failure to resuscitate will directly affect the cell state,
+ before forming the cells.
+ Some preparatory work needs to be done.
+ Put 15 milliliters centrifuge tubes, T25 cell culture flas
+ks, her pets,
+ Puppetta and other related items in the bios of decabinant
+ in advance.
+ Turn on the UV radiation to 30 minutes to disinfect all the
+ items.
+ During disinfection, preheat the water bath 37 degrees
+ Celsius and get a clean disposable pee
+ Glurv ready for use.
+ In the bios of decabinant, get a 15 milliliters sterile
+ centrifuge tube.
+ And add 9 milliliters of complete medium to it.
+ Put the tube on rack for later use.
+ Take out the cryovill with frozen cells from the liquid
+ nitrogen tank.
+ The resuscitation starts now.
+ Put the cryovill into the pee glove, submerge the glove
+ protected cryovill quickly in the water bath,
+ and check it constantly to speed up the melting for the
+ cells thoroughly in one minute.
+ Make sure that the cells are completely forward.
+ Stair all the cryovill with 75% ethanol and put it in the
+ bios of decabinant,
+ and the cells suspension in the cryovill to the former
+ prepared medium and mixed gently.
+ [Music]
+ Centrifuge the cells at 1,200 rpm approximately 250g to 3
+ minutes.
+ After centrifugation, we will see cell pellets at the
+ bottom of the tube.
+ Stair all the tube and put it in the bios of decabinant,
+ prepared the supernatant and discard it.
+ Add 5 milliliters of complete medium to resuscitate the
+ cells.
+ And gently prepare to mix.
+ After fully mixing, transfer the cell suspension to a T25
+ cell culture flask,
+ and well mark the flask, observe the cell status and seed
+ing density under a microscope.
+ Finally, put the flask into the incubator for culture and
+ make sure the water tray,
+ carbon dioxide concentration and temperature in the right
+ condition.
+ The resuscitation completes here.
+ In the end, we listed some related precautions in the
+ process.
+ Please refer to</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2510,6 +3514,103 @@
           <t>3DMK22osWVs</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[Music]
+ Welcome back to Cell Culture 101. In today's episode, we'll
+ dive into the fascinating world
+ of 3D cell culture, one of the most exciting advancements
+ in cell culture technology.
+ So, what exactly is 3D cell culture? Unlike traditional 2D
+ cell culture, which grows cells
+ on flat surfaces like Petri dishes, 3D cell culture allows
+ cells to grow in a 3-dimensional
+ environment. This technique has transformed how we study
+ cells, offering new insights into
+ biology and paving the way for breakthroughs in research
+ and medicine. First, let's talk
+ about why researchers are shifting from 2D to 3D cell
+ culture. While 2D models have been
+ the cornerstone of cell culture for decades, they come with
+ significant limitations.
+ Cell cells grow in 2D often behave differently than they
+ would in the body, where they
+ interact with complex 3D environments. This can lead to
+ results that don't fully represent
+ real-life biology. 3D cell culture, on the other hand, mim
+ics the natural and vivo
+ environment much more accurately. Cells can interact with
+ each other and their surroundings
+ in a way that closely resembles what happens in tissues and
+ organs. This makes 3D cell
+ culture an invaluable tool for drug testing, disease
+ modeling, and tissue engineering,
+ where understanding how cells behave in a realistic
+ environment is critical. There are
+ several methods researchers used to create 3D cell cultures
+, each with its own advantages.
+ One approach is scaffold-based systems, where cells are
+ grown on a supportive structure made
+ of materials like collagen or synthetic polymers. These
+ scaffolds help cells organize
+ into 3D shapes. Another method is scaffold-free systems,
+ where cells self-assemble and
+ destructors like spheroids, tiny spherical clusters of
+ cells that mimic tissues. We also
+ have hydredral systems, which use gel-like materials to
+ create a soft, tissue-like environment
+ for cells to grow. In addition to these, there are other
+ techniques like microcaribase
+ systems or bioreactive-based methods, which are especially
+ useful when scaling up 3D cultures
+ for industrial or clinical applications. These methods give
+ researchers the flexibility to
+ choose the best system based on their specific goals. The
+ applications of 3D cell culture
+ are revolutionizing multiple areas of research. In cancer
+ research, 3D tumor models are
+ being used to study how cancer spreads and response to
+ treatment. For example, spheroid models
+ can replicate the way tumors grow and interact with their
+ environment, providing insights
+ that 2D models simply can't. In regenerative medicine,
+ researchers are using 3D cell culture
+ to engineer tissues like skin, cartilage, and even more
+ complex structures like liver or heart
+ tissue. In personalized medicine, patient-derived cells are
+ grown in 3D to test drug responses
+ and designed tailored treatments. This has been especially
+ valuable in diseases like cancer,
+ individual patients may respond differently to the same
+ therapy. Even in neuroscience, 3D brain
+ organoids are being used to study brain development, neurod
+egenerative diseases like Alzheimer's
+ and the impact of drugs on the nervous system. It's no
+ wonder that 3D cell culture is becoming
+ a staple in biotech and pharmaceutical research. Looking
+ ahead, the possibilities for 3D cell
+ culture are incredibly exciting. One emerging technology is
+ organonotyp systems, which combine
+ 3D cell culture with microfluidics to create miniature
+ functional models of organs. These systems
+ allow researchers to study how organs interact with drugs
+ or diseases in real time. Another area
+ of innovation is 3D bioprinting, where researchers use
+ specialized printers to build complex
+ tissue structures layer by layer. This could eventually
+ lead to fully functional lab-grown organs
+ for transplantation. As these technologies continue to
+ advance, 3D cell culture will play a
+ central role in tackling some of the biggest challenges in
+ medicine from curing cancer to combating
+ organ shortages. Thank you for joining me in today's
+ episode of Cell Culture 101. Stay tuned.
+ This is just the beginning. In future videos, we'll explore
+ more aspects of cell culture,
+ from the basics to cutting-edge techniques. Don't forget to
+ subscribe and I'll see you next time.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2565,6 +3666,84 @@
           <t>wGR1OmaCFBU</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[Music]
+ Hey everyone! Today I'm going to talk about a technique
+ that's super important in
+ cell culture, cryopreservation. It's a crucial process that
+ helps preserve cells, tissues,
+ and even entire organisms at very low temperatures, and it
+'s especially useful in research
+ and clinical applications. So, what exactly is cryopres
+ervation? Well, it's the process of freezing
+ biological samples, like cells, stem cells, sperm, or embry
+os, using liquid nitrogen to stop
+ all biological activity. This prevents the cells from
+ degrading over time, but it's not as simple
+ as just freezing everything. If done wrong, it can actually
+ cause damage to the cells which
+ is why it's so important to get it right. Cryopreservation
+ is essential for storing biological
+ materials long-term. For example, if we want to keep stem
+ cells or sperm for future use, cryopreservation
+ helps ensure they stay viable when we need them. It's
+ especially key in places like fertility
+ treatments or biobanking where we need to preserve the
+ quality of the cells for later. Now, let's
+ talk about how to actually do it the right way. First up,
+ we need to prepare the sample properly.
+ You may not know this, but most biological materials are
+ made up of water, and when water freezes,
+ it expands. If cells freeze without the right precautions,
+ ice crystals conform inside,
+ and damage the cell membrane. So, to prevent this, we use a
+ freezing medium, things like
+ dimethyl sulfoxide, that helps protect the cells during the
+ freezing process. It's important to
+ get the concentration of the freezing medium just right.
+ Too much can actually be toxic to the cells,
+ so it's crucial to find the right balance. If you're unsure
+, don't hesitate to reach out.
+ We're happy to provide free technical support to guide you
+ through it. Once the cells are prepared,
+ we need to freeze them gradually. Freezing too quickly can
+ cause uneven cooling,
+ which could damage the cells. Ideally, we use a controlled
+ rate freezer, which cools the cells slowly
+ and evenly. If a freezing container is not available, you
+ can manually freeze the cells by sequentially
+ placing the cryovules at 2 to 8 degrees Celsius for about
+ 40 minutes, then at -20 degrees
+ Celsius for 30 to 60 minutes, and finally at -80 degrees
+ Celsius overnight. After the cells are frozen,
+ they're stored in liquid nitrogen at -196 degrees Celsius.
+ This super low temperature essentially
+ stops all biological activity, keeping the cells preserved
+ until we need them again. But freezing
+ is only half the battle. Thawing is just as important. If
+ you don't throw the cells carefully,
+ you could end up causing even more damage. The key is to
+ throw the cells rapidly,
+ usually in a water bath at 37 degrees Celsius. This helps
+ prevent ice crystals from forming again.
+ You also need to handle the sample gently as any rough
+ handling can harm the cells.
+ Once the cells are thought, it's time to remove the
+ freezing medium. This is done gradually
+ to avoid exposing the cells to too much cryoprotectant,
+ which can be harmful as they recover.
+ So, to sum it up, cryopreservation requires careful
+ preparation with the right freezing medium,
+ gradual freezing and gentle thawing. When done properly, it
+ preserves the cells for future use.
+ But even small mistakes in the process can lead to damage,
+ so it's really important to follow
+ the steps carefully. If you found this video helpful, make
+ sure to like and follow
+ for more tips on cell culture. Thanks for watching!</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2620,6 +3799,19 @@
           <t>gJ1qtdkZeIw</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Every discovery begins with a decision to trust the
+ materials you use in the process is behind them.
+ From sourcing to validation, we ensure every material meets
+ the standards your research demands,
+ because like you, we know there's no room for compromise.
+ It's not just about the raw materials, it's about the
+ foundation of trust we build into every batch.
+ Trust that matches the care you bring to your work.
+ You care about starting with the best, so to wait.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2675,6 +3867,23 @@
           <t>Z9eAVNXITyo</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Precision doesn't just happen, it's built.
+ Built on systems that eliminate uncertainty,
+ so you can focus on innovation.
+ Every motion, every process is designed to create
+ consistency.
+ To build trust into every batch,
+ just as you build trust into every experiment.
+ Because automation isn't just about efficiency,
+ it's about reliability,
+ about ensuring that what starts perfect,
+ stays perfect from our systems to your hands.
+ You rely on precision to achieve consistency.
+ So do we.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2730,6 +3939,33 @@
           <t>vGVQ2gwfmJA</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[MUSIC]
+ Procell is equipped with multiple sets of fully automatic
+ sterile systems,
+ consisted of medium preparation, filling and packaging
+ modules,
+ to produce over 9,000 bottles of products with monitored
+ and controllable process.
+ Using mass production and multi-stage filtration, Procell
+ ensures absolute sterility,
+ higher stability, and minimum intercoefficient of variation
+.
+ [MUSIC]
+ All products of Procell are proved to have no bacteria, bun
+gei,
+ microplasma, or other microbial contamination.
+ Test includes strict quality control system, including
+ microbial detection,
+ cell growth test, growth curve flooding, and four times of
+ lamp inspection.
+ The produced culture media are with low endotoxin, good
+ cell supporting, and stable quality.
+ [MUSIC]
+ [MUSIC]</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2785,6 +4021,21 @@
           <t>edDwoZclQP0</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storility isn't just a process, it's a promise.
+ A promise to protect your work, your results, and your
+ vision for what's possible.
+ Every step we take is designed to eliminate down,
+ to safeguard the purity you need for the work that matters
+ most.
+ Because we know that Storility isn't optional,
+ it's the foundation of every breakthrough, every discovery,
+ purity and every drop.
+ Because you care so do we.
+ (gentle music)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2840,6 +4091,22 @@
           <t>QjPcu8QRkEE</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>When your experiments depend on precision,
+ you trust that what arrives at your lab is as perfect as
+ the moment it left ours.
+ From the sterile filling process to tamper proof packaging
+ and temperature-controlled delivery,
+ we design every step with your research in mind.
+ We don't just deliver products, we deliver trust.
+ Trust that every reagent is traceable, safe, and ready for
+ the work that changes the world.
+ Because what matters to you isn't just the product.
+ It's everything it helps you achieve.
+ You care about every detail, so do we.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2893,6 +4160,69 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>PPIy7noBCgU</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Microplasma rapid detection kit operation guide.
+ This protocol demonstrates a PCR-based workflow for micropl
+asma rapid detection kit.
+ PCR amplification, culture the cells for about 48 to 72
+ hours, then harvest when they reach
+ around 80 percent confidence.
+ Thought all kit components at 40 g Celsius for 2 hours, or
+ at room temperature for 30 minutes
+ prior to use.
+ In the centrifuge of 1000 revolutions per minute for 1
+ minute to collect the liquid at the bottom
+ of the tube.
+ Prepare 6 PCR tubes, arranged into 3 groups with 2 parallel
+ reactions per group, to compensate
+ for pipetting loss, prepare a PCR reaction system for 8
+ reactions.
+ In a 2-millimeter centrifuge tube, sequentially add tech
+ PCR master mix, micro-free water,
+ and primer mix.
+ Mix thoroughly by pipetting to prepare the PCR reaction
+ mixture.
+ At 18 micro-lighters of PCR reaction mixture, teach PCR
+ tube in the test, positive control
+ and negative control groups.
+ Add the corresponding samples to each PCR tube and mix
+ gently by pipetting.
+ Add the PCR reaction mixture to the PCR reaction mixture
+ and mix gently by pipetting.
+ Briefly centrifuge the PCR tubes.
+ Place the PCR tubes in a thermal cycler and run the ampl
+ification using the preset program.
+ After amplification, remove the PCR tubes, analyze the PCR
+ products by agarose gel electrophoresis.
+ Gile electrophoresis, and insert the comb into the
+ designated slots.
+ Add 67 milliliters of 0.5 times TBE buffer to a conical fl
+ask and add agarose to prepare
+ a 1% to 1.5% agarose gel.
+ Heat in a microwave for approximately 2 minutes until the
+ agarose is completely dissolved.
+ Add the nucleic acid stain and mix thoroughly.
+ Slowly pour the solution into the casting tray to form a
+ uniform gel layer.
+ Allow the gel to solidify at room temperature for about 1
+ hour, gently remove the comb vertically.
+ Place the gel into the electrophoresis tank.
+ Add 0.5 times TBE buffer until the gel is fully submerged.
+ Load the PCR products into the wells 10 microliders per
+ well.
+ Set the voltage to 160 volts and run electrophoresis for 15
+ minutes.
+ Stop the electrophoresis and remove the gel.
+ Capture images using a gel documentation system and save
+ the results.
+ Determine whether the samples contain microplasma
+ contamination by comparing the results of the positive and
+ negative controls.
+ The expected amplicon size is approximately 500 base pairs
+ with slight variation depending on the species.</t>
         </is>
       </c>
     </row>
